--- a/Data/metadaten_grafiken_kantonale_abstimmungen.xlsx
+++ b/Data/metadaten_grafiken_kantonale_abstimmungen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60387dca0f89eeaf/SDA_eidgenoessische_abstimmungen/20260614_LENA_Abstimmungen/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60387dca0f89eeaf/SDA_eidgenoessische_abstimmungen/20260927_LENA_Abstimmungen/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_CFBC576EC3574AFC124848D2425A198B17466879" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4625AC29-C321-44E4-8FF2-37C5F8B90693}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_CFBC576EC3574AFC124848D2425A198B17466879" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F06D87-7570-4E4B-B536-9AAEED1D410A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Karten" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="135">
   <si>
     <t>Typ</t>
   </si>
@@ -56,18 +56,12 @@
     <t>LU</t>
   </si>
   <si>
-    <t>SO</t>
-  </si>
-  <si>
     <t>BL</t>
   </si>
   <si>
     <t>SH</t>
   </si>
   <si>
-    <t>SG</t>
-  </si>
-  <si>
     <t>GE</t>
   </si>
   <si>
@@ -80,433 +74,358 @@
     <t>it-CH</t>
   </si>
   <si>
-    <t>AG</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
     <t>ZH</t>
   </si>
   <si>
-    <t>ZH: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>EChE2</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/EChE2/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="ZH: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-EChE2" src="https://datawrapper.dwcdn.net/EChE2/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-EChE2"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/EChE2/embed.js" charset="utf-8" data-target="#datawrapper-vis-EChE2"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/EChE2/full.png?unq=keystone-sda" alt="ZH: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>BE</t>
   </si>
   <si>
-    <t>BE: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>vFOa1</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/vFOa1/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BE: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-vFOa1" src="https://datawrapper.dwcdn.net/vFOa1/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-vFOa1"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/vFOa1/embed.js" charset="utf-8" data-target="#datawrapper-vis-vFOa1"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/vFOa1/full.png?unq=keystone-sda" alt="BE: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BE: Votations cantonales du 14 juin 2026</t>
-  </si>
-  <si>
-    <t>Hxsod</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/Hxsod/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BE: Votations cantonales du 14 juin 2026" aria-label="Barres empilées" id="datawrapper-chart-Hxsod" src="https://datawrapper.dwcdn.net/Hxsod/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:452px" id="datawrapper-vis-Hxsod"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Hxsod/embed.js" charset="utf-8" data-target="#datawrapper-vis-Hxsod"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Hxsod/full.png?unq=keystone-sda" alt="BE: Votations cantonales du 14 juin 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>LU: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>Z1lYv</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/Z1lYv/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="LU: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-Z1lYv" src="https://datawrapper.dwcdn.net/Z1lYv/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-Z1lYv"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Z1lYv/embed.js" charset="utf-8" data-target="#datawrapper-vis-Z1lYv"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Z1lYv/full.png?unq=keystone-sda" alt="LU: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SZ</t>
-  </si>
-  <si>
-    <t>SZ: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>yfox1</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/yfox1/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SZ: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-yfox1" src="https://datawrapper.dwcdn.net/yfox1/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-yfox1"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/yfox1/embed.js" charset="utf-8" data-target="#datawrapper-vis-yfox1"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/yfox1/full.png?unq=keystone-sda" alt="SZ: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>NW</t>
-  </si>
-  <si>
-    <t>NW: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>IJ62V</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/IJ62V/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NW: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-IJ62V" src="https://datawrapper.dwcdn.net/IJ62V/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-IJ62V"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/IJ62V/embed.js" charset="utf-8" data-target="#datawrapper-vis-IJ62V"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/IJ62V/full.png?unq=keystone-sda" alt="NW: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SO: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>nQFbq</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/nQFbq/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SO: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-nQFbq" src="https://datawrapper.dwcdn.net/nQFbq/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-nQFbq"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/nQFbq/embed.js" charset="utf-8" data-target="#datawrapper-vis-nQFbq"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/nQFbq/full.png?unq=keystone-sda" alt="SO: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>BS</t>
   </si>
   <si>
-    <t>BS: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>unPGW</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/unPGW/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BS: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-unPGW" src="https://datawrapper.dwcdn.net/unPGW/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-unPGW"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/unPGW/embed.js" charset="utf-8" data-target="#datawrapper-vis-unPGW"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/unPGW/full.png?unq=keystone-sda" alt="BS: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BL: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>zYfAO</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/zYfAO/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BL: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-zYfAO" src="https://datawrapper.dwcdn.net/zYfAO/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-zYfAO"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/zYfAO/embed.js" charset="utf-8" data-target="#datawrapper-vis-zYfAO"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/zYfAO/full.png?unq=keystone-sda" alt="BL: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SH: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>oDIVe</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/oDIVe/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SH: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-oDIVe" src="https://datawrapper.dwcdn.net/oDIVe/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-oDIVe"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/oDIVe/embed.js" charset="utf-8" data-target="#datawrapper-vis-oDIVe"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/oDIVe/full.png?unq=keystone-sda" alt="SH: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SG: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>PZJ3C</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/PZJ3C/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SG: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-PZJ3C" src="https://datawrapper.dwcdn.net/PZJ3C/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-PZJ3C"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/PZJ3C/embed.js" charset="utf-8" data-target="#datawrapper-vis-PZJ3C"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/PZJ3C/full.png?unq=keystone-sda" alt="SG: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>AG: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>zxRJ7</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/zxRJ7/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AG: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-zxRJ7" src="https://datawrapper.dwcdn.net/zxRJ7/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-zxRJ7"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/zxRJ7/embed.js" charset="utf-8" data-target="#datawrapper-vis-zxRJ7"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/zxRJ7/full.png?unq=keystone-sda" alt="AG: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>TG: Kantonale Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>o3gPH</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/o3gPH/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="TG: Kantonale Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-o3gPH" src="https://datawrapper.dwcdn.net/o3gPH/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-o3gPH"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/o3gPH/embed.js" charset="utf-8" data-target="#datawrapper-vis-o3gPH"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/o3gPH/full.png?unq=keystone-sda" alt="TG: Kantonale Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>TI: Votazione cantonale del 14 giugno 2026</t>
-  </si>
-  <si>
-    <t>pHmUb</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/pHmUb/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="TI: Votazione cantonale del 14 giugno 2026" aria-label="Barre impilate" id="datawrapper-chart-pHmUb" src="https://datawrapper.dwcdn.net/pHmUb/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-pHmUb"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/pHmUb/embed.js" charset="utf-8" data-target="#datawrapper-vis-pHmUb"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/pHmUb/full.png?unq=keystone-sda" alt="TI: Votazione cantonale del 14 giugno 2026 (Barre impilate)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>VD</t>
   </si>
   <si>
-    <t>VD: Votations cantonales du 14 juin 2026</t>
-  </si>
-  <si>
-    <t>FsKx7</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/FsKx7/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VD: Votations cantonales du 14 juin 2026" aria-label="Barres empilées" id="datawrapper-chart-FsKx7" src="https://datawrapper.dwcdn.net/FsKx7/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:452px" id="datawrapper-vis-FsKx7"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/FsKx7/embed.js" charset="utf-8" data-target="#datawrapper-vis-FsKx7"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/FsKx7/full.png?unq=keystone-sda" alt="VD: Votations cantonales du 14 juin 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>NE: Votations cantonales du 14 juin 2026</t>
-  </si>
-  <si>
-    <t>U01b5</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/U01b5/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NE: Votations cantonales du 14 juin 2026" aria-label="Barres empilées" id="datawrapper-chart-U01b5" src="https://datawrapper.dwcdn.net/U01b5/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:452px" id="datawrapper-vis-U01b5"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/U01b5/embed.js" charset="utf-8" data-target="#datawrapper-vis-U01b5"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/U01b5/full.png?unq=keystone-sda" alt="NE: Votations cantonales du 14 juin 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GE: Votations cantonales du 14 juin 2026</t>
-  </si>
-  <si>
-    <t>0rMCS</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/0rMCS/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GE: Votations cantonales du 14 juin 2026" aria-label="Barres empilées" id="datawrapper-chart-0rMCS" src="https://datawrapper.dwcdn.net/0rMCS/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:452px" id="datawrapper-vis-0rMCS"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/0rMCS/embed.js" charset="utf-8" data-target="#datawrapper-vis-0rMCS"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/0rMCS/full.png?unq=keystone-sda" alt="GE: Votations cantonales du 14 juin 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SZ_Praemienverbilligung</t>
-  </si>
-  <si>
-    <t>SZ: Volksinitiative «Kaufkraft stärken – Prämienverbilligung auch für den Mittelstand»</t>
-  </si>
-  <si>
-    <t>WseAC</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/WseAC/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SZ: Volksinitiative «Kaufkraft stärken – Prämienverbilligung auch für den Mittelstand»" aria-label="Choroplethen-Karte" id="datawrapper-chart-WseAC" src="https://datawrapper.dwcdn.net/WseAC/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-WseAC"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/WseAC/embed.js" charset="utf-8" data-target="#datawrapper-vis-WseAC"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/WseAC/full.png?unq=keystone-sda" alt="SZ: Volksinitiative «Kaufkraft stärken – Prämienverbilligung auch für den Mittelstand» (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GE_signes_religieux</t>
-  </si>
-  <si>
-    <t>GE: Loi pour une expression non ostentatoire des convictions religieuses</t>
-  </si>
-  <si>
-    <t>pTMW8</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/pTMW8/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GE: Loi pour une expression non ostentatoire des convictions religieuses" aria-label="Carte choroplèthe" id="datawrapper-chart-pTMW8" src="https://datawrapper.dwcdn.net/pTMW8/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-pTMW8"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/pTMW8/embed.js" charset="utf-8" data-target="#datawrapper-vis-pTMW8"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/pTMW8/full.png?unq=keystone-sda" alt="GE: Loi pour une expression non ostentatoire des convictions religieuses (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GE_LHOM</t>
-  </si>
-  <si>
-    <t>GE: Loi sur les heures d'ouverture des magasins</t>
-  </si>
-  <si>
-    <t>h9IH0</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/h9IH0/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GE: Loi sur les heures d'ouverture des magasins" aria-label="Carte choroplèthe" id="datawrapper-chart-h9IH0" src="https://datawrapper.dwcdn.net/h9IH0/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-h9IH0"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/h9IH0/embed.js" charset="utf-8" data-target="#datawrapper-vis-h9IH0"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/h9IH0/full.png?unq=keystone-sda" alt="GE: Loi sur les heures d'ouverture des magasins (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>NE_droit_aines</t>
-  </si>
-  <si>
-    <t>NE: La reconnaissance des aînées et des aînés dans la Constitution</t>
-  </si>
-  <si>
-    <t>beRZ6</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/beRZ6/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NE: La reconnaissance des aînées et des aînés dans la Constitution" aria-label="Carte choroplèthe" id="datawrapper-chart-beRZ6" src="https://datawrapper.dwcdn.net/beRZ6/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-beRZ6"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/beRZ6/embed.js" charset="utf-8" data-target="#datawrapper-vis-beRZ6"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/beRZ6/full.png?unq=keystone-sda" alt="NE: La reconnaissance des aînées et des aînés dans la Constitution (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>VD_salaire_minimum_const</t>
-  </si>
-  <si>
-    <t>VD: Initiative populaire constitutionnelle « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal »</t>
-  </si>
-  <si>
-    <t>JTf9z</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/JTf9z/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VD: Initiative populaire constitutionnelle « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal »" aria-label="Carte choroplèthe" id="datawrapper-chart-JTf9z" src="https://datawrapper.dwcdn.net/JTf9z/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-JTf9z"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/JTf9z/embed.js" charset="utf-8" data-target="#datawrapper-vis-JTf9z"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/JTf9z/full.png?unq=keystone-sda" alt="VD: Initiative populaire constitutionnelle « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal » (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>ZH_Wohnungsinitiative</t>
-  </si>
-  <si>
-    <t>Wohnungsinitiative</t>
-  </si>
-  <si>
-    <t>DpvP9</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/DpvP9/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Wohnungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-DpvP9" src="https://datawrapper.dwcdn.net/DpvP9/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="688" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:688px" id="datawrapper-vis-DpvP9"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/DpvP9/embed.js" charset="utf-8" data-target="#datawrapper-vis-DpvP9"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/DpvP9/full.png?unq=keystone-sda" alt="Wohnungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>ZH_Wohnschutzinitiative</t>
-  </si>
-  <si>
-    <t>Wohnschutz-Initiative</t>
-  </si>
-  <si>
-    <t>iqK6z</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/iqK6z/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Wohnschutz-Initiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-iqK6z" src="https://datawrapper.dwcdn.net/iqK6z/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="688" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:688px" id="datawrapper-vis-iqK6z"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/iqK6z/embed.js" charset="utf-8" data-target="#datawrapper-vis-iqK6z"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/iqK6z/full.png?unq=keystone-sda" alt="Wohnschutz-Initiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>VD_salaire_minimum_23</t>
-  </si>
-  <si>
-    <t>Initiative populaire législative « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal »</t>
-  </si>
-  <si>
-    <t>82JFI</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/82JFI/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Initiative populaire législative « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal »" aria-label="Carte choroplèthe" id="datawrapper-chart-82JFI" src="https://datawrapper.dwcdn.net/82JFI/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="542" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:542px" id="datawrapper-vis-82JFI"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/82JFI/embed.js" charset="utf-8" data-target="#datawrapper-vis-82JFI"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/82JFI/full.png?unq=keystone-sda" alt="Initiative populaire législative « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal » (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+    <t>BE_formation</t>
+  </si>
+  <si>
+    <t>BE: Volksinitiative «Berner Bildungsinitiative»</t>
+  </si>
+  <si>
+    <t>oyyOs</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/oyyOs/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Volksinitiative «Berner Bildungsinitiative»" aria-label="Choroplethen-Karte" id="datawrapper-chart-oyyOs" src="https://datawrapper.dwcdn.net/oyyOs/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-oyyOs"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/oyyOs/embed.js" charset="utf-8" data-target="#datawrapper-vis-oyyOs"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/oyyOs/full.png?unq=keystone-sda" alt="BE: Volksinitiative «Berner Bildungsinitiative» (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Initiative sur la formation</t>
+  </si>
+  <si>
+    <t>gQVcw</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/gQVcw/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Initiative sur la formation" aria-label="Carte choroplèthe" id="datawrapper-chart-gQVcw" src="https://datawrapper.dwcdn.net/gQVcw/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-gQVcw"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/gQVcw/embed.js" charset="utf-8" data-target="#datawrapper-vis-gQVcw"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/gQVcw/full.png?unq=keystone-sda" alt="BE: Initiative sur la formation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VD_impots_12</t>
+  </si>
+  <si>
+    <t>VD: Initiative populaire dite des 12%</t>
+  </si>
+  <si>
+    <t>d3Io2</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/d3Io2/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VD: Initiative populaire dite des 12%" aria-label="Carte choroplèthe" id="datawrapper-chart-d3Io2" src="https://datawrapper.dwcdn.net/d3Io2/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-d3Io2"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/d3Io2/embed.js" charset="utf-8" data-target="#datawrapper-vis-d3Io2"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/d3Io2/full.png?unq=keystone-sda" alt="VD: Initiative populaire dite des 12% (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE_contraception</t>
+  </si>
+  <si>
+    <t>GE: Initiative "pour une contraception gratuite"</t>
+  </si>
+  <si>
+    <t>SfH0L</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/SfH0L/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Initiative &amp;quot;pour une contraception gratuite&amp;quot;" aria-label="Carte choroplèthe" id="datawrapper-chart-SfH0L" src="https://datawrapper.dwcdn.net/SfH0L/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-SfH0L"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/SfH0L/embed.js" charset="utf-8" data-target="#datawrapper-vis-SfH0L"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/SfH0L/full.png?unq=keystone-sda" alt="GE: Initiative &amp;quot;pour une contraception gratuite&amp;quot; (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE_credit_projets_transfrontaliers</t>
+  </si>
+  <si>
+    <t>GE: Crédit pour la réalisation de projets transfrontaliers</t>
+  </si>
+  <si>
+    <t>6pZMD</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/6pZMD/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Crédit pour la réalisation de projets transfrontaliers" aria-label="Carte choroplèthe" id="datawrapper-chart-6pZMD" src="https://datawrapper.dwcdn.net/6pZMD/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-6pZMD"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/6pZMD/embed.js" charset="utf-8" data-target="#datawrapper-vis-6pZMD"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/6pZMD/full.png?unq=keystone-sda" alt="GE: Crédit pour la réalisation de projets transfrontaliers (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE_locataires</t>
+  </si>
+  <si>
+    <t>GE: Modification de loi pour permettre à un locataire d'acheter son logement</t>
+  </si>
+  <si>
+    <t>zTJLI</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/zTJLI/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Modification de loi pour permettre à un locataire d'acheter son logement" aria-label="Carte choroplèthe" id="datawrapper-chart-zTJLI" src="https://datawrapper.dwcdn.net/zTJLI/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-zTJLI"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/zTJLI/embed.js" charset="utf-8" data-target="#datawrapper-vis-zTJLI"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/zTJLI/full.png?unq=keystone-sda" alt="GE: Modification de loi pour permettre à un locataire d'acheter son logement (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE_HES</t>
+  </si>
+  <si>
+    <t>GE: Coupe cantonale de 2 millions de francs envers la HES-SO Genève</t>
+  </si>
+  <si>
+    <t>Wv1Sh</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/Wv1Sh/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Coupe cantonale de 2 millions de francs envers la HES-SO Genève" aria-label="Carte choroplèthe" id="datawrapper-chart-Wv1Sh" src="https://datawrapper.dwcdn.net/Wv1Sh/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-Wv1Sh"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Wv1Sh/embed.js" charset="utf-8" data-target="#datawrapper-vis-Wv1Sh"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Wv1Sh/full.png?unq=keystone-sda" alt="GE: Coupe cantonale de 2 millions de francs envers la HES-SO Genève (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR_Stimmrechtsalter_16</t>
+  </si>
+  <si>
+    <t>GR: Teilrevision der Verfassung des Kantons Graubünden (Stimmrechtsalter 16)</t>
+  </si>
+  <si>
+    <t>8PTNn</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/8PTNn/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Teilrevision der Verfassung des Kantons Graubünden (Stimmrechtsalter 16)" aria-label="Choroplethen-Karte" id="datawrapper-chart-8PTNn" src="https://datawrapper.dwcdn.net/8PTNn/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:494px" id="datawrapper-vis-8PTNn"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/8PTNn/embed.js" charset="utf-8" data-target="#datawrapper-vis-8PTNn"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/8PTNn/full.png?unq=keystone-sda" alt="GR: Teilrevision der Verfassung des Kantons Graubünden (Stimmrechtsalter 16) (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR: Revisione parziale della Costituzione del Cantone dei Grigioni (diritto di voto a 16 anni)</t>
+  </si>
+  <si>
+    <t>hC1Ps</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/hC1Ps/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Revisione parziale della Costituzione del Cantone dei Grigioni (diritto di voto a 16 anni)" aria-label="Mappa coropletica" id="datawrapper-chart-hC1Ps" src="https://datawrapper.dwcdn.net/hC1Ps/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:534px" id="datawrapper-vis-hC1Ps"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/hC1Ps/embed.js" charset="utf-8" data-target="#datawrapper-vis-hC1Ps"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/hC1Ps/full.png?unq=keystone-sda" alt="GR: Revisione parziale della Costituzione del Cantone dei Grigioni (diritto di voto a 16 anni) (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>LU_Fan-Gewalt-Initiative</t>
+  </si>
+  <si>
+    <t>Volksinitiative «Gegen Fan-Gewalt»</t>
+  </si>
+  <si>
+    <t>QCddo</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/QCddo/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Volksinitiative «Gegen Fan-Gewalt»" aria-label="Choroplethen-Karte" id="datawrapper-chart-QCddo" src="https://datawrapper.dwcdn.net/QCddo/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="348" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:348px" id="datawrapper-vis-QCddo"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/QCddo/embed.js" charset="utf-8" data-target="#datawrapper-vis-QCddo"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/QCddo/full.png?unq=keystone-sda" alt="Volksinitiative «Gegen Fan-Gewalt» (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>ZH: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>790kN</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/790kN/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="ZH: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-790kN" src="https://datawrapper.dwcdn.net/790kN/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-790kN"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/790kN/embed.js" charset="utf-8" data-target="#datawrapper-vis-790kN"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/790kN/full.png?unq=keystone-sda" alt="ZH: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>rzo8a</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/rzo8a/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-rzo8a" src="https://datawrapper.dwcdn.net/rzo8a/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-rzo8a"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/rzo8a/embed.js" charset="utf-8" data-target="#datawrapper-vis-rzo8a"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/rzo8a/full.png?unq=keystone-sda" alt="BE: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Votations cantonales du 27 septembre 2026</t>
+  </si>
+  <si>
+    <t>ncfsY</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/ncfsY/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Votations cantonales du 27 septembre 2026" aria-label="Barres empilées" id="datawrapper-chart-ncfsY" src="https://datawrapper.dwcdn.net/ncfsY/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:452px" id="datawrapper-vis-ncfsY"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ncfsY/embed.js" charset="utf-8" data-target="#datawrapper-vis-ncfsY"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ncfsY/full.png?unq=keystone-sda" alt="BE: Votations cantonales du 27 septembre 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>LU: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>9D6Uy</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/9D6Uy/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="LU: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-9D6Uy" src="https://datawrapper.dwcdn.net/9D6Uy/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-9D6Uy"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/9D6Uy/embed.js" charset="utf-8" data-target="#datawrapper-vis-9D6Uy"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/9D6Uy/full.png?unq=keystone-sda" alt="LU: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BS: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>FKuft</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/FKuft/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BS: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-FKuft" src="https://datawrapper.dwcdn.net/FKuft/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-FKuft"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/FKuft/embed.js" charset="utf-8" data-target="#datawrapper-vis-FKuft"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/FKuft/full.png?unq=keystone-sda" alt="BS: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BL: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>XpAOy</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/XpAOy/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BL: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-XpAOy" src="https://datawrapper.dwcdn.net/XpAOy/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-XpAOy"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/XpAOy/embed.js" charset="utf-8" data-target="#datawrapper-vis-XpAOy"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/XpAOy/full.png?unq=keystone-sda" alt="BL: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SH: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>eCBvW</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/eCBvW/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SH: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-eCBvW" src="https://datawrapper.dwcdn.net/eCBvW/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-eCBvW"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/eCBvW/embed.js" charset="utf-8" data-target="#datawrapper-vis-eCBvW"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/eCBvW/full.png?unq=keystone-sda" alt="SH: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>GR: Kantonale Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>2URsq</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/2URsq/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Kantonale Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-2URsq" src="https://datawrapper.dwcdn.net/2URsq/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-2URsq"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/2URsq/embed.js" charset="utf-8" data-target="#datawrapper-vis-2URsq"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/2URsq/full.png?unq=keystone-sda" alt="GR: Kantonale Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR: Votazione cantonale del 27 settembre 2026</t>
+  </si>
+  <si>
+    <t>1G9Ih</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/1G9Ih/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Votazione cantonale del 27 settembre 2026" aria-label="Barre impilate" id="datawrapper-chart-1G9Ih" src="https://datawrapper.dwcdn.net/1G9Ih/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-1G9Ih"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/1G9Ih/embed.js" charset="utf-8" data-target="#datawrapper-vis-1G9Ih"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/1G9Ih/full.png?unq=keystone-sda" alt="GR: Votazione cantonale del 27 settembre 2026 (Barre impilate)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VD: Votations cantonales du 27 septembre 2026</t>
+  </si>
+  <si>
+    <t>cVksP</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/cVksP/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VD: Votations cantonales du 27 septembre 2026" aria-label="Barres empilées" id="datawrapper-chart-cVksP" src="https://datawrapper.dwcdn.net/cVksP/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:452px" id="datawrapper-vis-cVksP"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/cVksP/embed.js" charset="utf-8" data-target="#datawrapper-vis-cVksP"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/cVksP/full.png?unq=keystone-sda" alt="VD: Votations cantonales du 27 septembre 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE: Votations cantonales du 27 septembre 2026</t>
+  </si>
+  <si>
+    <t>ZpF6E</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/ZpF6E/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Votations cantonales du 27 septembre 2026" aria-label="Barres empilées" id="datawrapper-chart-ZpF6E" src="https://datawrapper.dwcdn.net/ZpF6E/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:452px" id="datawrapper-vis-ZpF6E"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ZpF6E/embed.js" charset="utf-8" data-target="#datawrapper-vis-ZpF6E"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ZpF6E/full.png?unq=keystone-sda" alt="GE: Votations cantonales du 27 septembre 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
   </si>
 </sst>
 </file>
@@ -893,12 +812,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="114.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.7109375" bestFit="1" customWidth="1"/>
@@ -935,25 +854,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -961,25 +880,25 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -987,25 +906,25 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1013,25 +932,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1039,25 +958,25 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1065,25 +984,25 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1091,25 +1010,25 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1117,25 +1036,77 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="E9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H9" t="s">
-        <v>149</v>
+      <c r="E10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1148,12 +1119,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987586D8-8C04-4B25-A287-87D0FE2E9E08}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -1190,25 +1161,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>82</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>83</v>
-      </c>
-      <c r="G2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1216,25 +1187,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1242,25 +1213,25 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1268,25 +1239,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1294,25 +1265,25 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1320,25 +1291,25 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1346,25 +1317,25 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1372,25 +1343,25 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H9" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1398,25 +1369,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1424,25 +1395,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1453,183 +1424,27 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="H12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H18">
-    <sortCondition ref="B2:B18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H11">
+    <sortCondition ref="B2:B11"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
